--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P8" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O8" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P8" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P9" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P8" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P9" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O8" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P8" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P9" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.61</v>
+        <v>1.96</v>
       </c>
       <c r="O3" t="n">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="P3" t="n">
-        <v>2.43</v>
+        <v>3.41</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.34</v>
+        <v>2.51</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="P4" t="n">
-        <v>2.83</v>
+        <v>2.58</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.96</v>
+        <v>2.34</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>3.41</v>
+        <v>2.83</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.51</v>
+        <v>2.61</v>
       </c>
       <c r="O6" t="n">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="P6" t="n">
-        <v>2.58</v>
+        <v>2.43</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P8" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P9" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="O2" t="n">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="O3" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="P3" t="n">
-        <v>3.41</v>
+        <v>2.89</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.83</v>
+        <v>3.41</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.34</v>
+        <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="P2" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="O3" t="n">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.61</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="P6" t="n">
-        <v>2.43</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O8" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P8" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P9" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.61</v>
+        <v>2.34</v>
       </c>
       <c r="O2" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.34</v>
+        <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="P3" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.51</v>
+        <v>1.96</v>
       </c>
       <c r="O4" t="n">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="P4" t="n">
-        <v>2.58</v>
+        <v>3.41</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="P5" t="n">
-        <v>3.41</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="O6" t="n">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>2.58</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P2" t="n">
-        <v>2.83</v>
+        <v>3.41</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.61</v>
+        <v>2.25</v>
       </c>
       <c r="O3" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="P3" t="n">
-        <v>2.43</v>
+        <v>2.89</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.96</v>
+        <v>2.51</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="P4" t="n">
-        <v>3.41</v>
+        <v>2.58</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="O5" t="n">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.51</v>
+        <v>2.61</v>
       </c>
       <c r="O6" t="n">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="P6" t="n">
-        <v>2.58</v>
+        <v>2.43</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P8" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P9" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.96</v>
+        <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="P2" t="n">
-        <v>3.41</v>
+        <v>2.43</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.51</v>
+        <v>1.96</v>
       </c>
       <c r="O4" t="n">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="P4" t="n">
-        <v>2.58</v>
+        <v>3.41</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.34</v>
+        <v>2.51</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="P5" t="n">
-        <v>2.83</v>
+        <v>2.58</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.61</v>
+        <v>2.34</v>
       </c>
       <c r="O6" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="P6" t="n">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O8" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P8" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P9" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.61</v>
+        <v>2.25</v>
       </c>
       <c r="O2" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="P2" t="n">
-        <v>2.43</v>
+        <v>2.89</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="O3" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="P3" t="n">
-        <v>2.89</v>
+        <v>3.41</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.96</v>
+        <v>2.51</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="P4" t="n">
-        <v>3.41</v>
+        <v>2.58</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.51</v>
+        <v>2.61</v>
       </c>
       <c r="O5" t="n">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="P5" t="n">
-        <v>2.58</v>
+        <v>2.43</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P8" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P9" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="O2" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="P2" t="n">
-        <v>2.89</v>
+        <v>3.41</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.96</v>
+        <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="P3" t="n">
-        <v>3.41</v>
+        <v>2.43</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P4" t="n">
-        <v>2.58</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.61</v>
+        <v>2.34</v>
       </c>
       <c r="O5" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.34</v>
+        <v>2.51</v>
       </c>
       <c r="O6" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="P6" t="n">
-        <v>2.83</v>
+        <v>2.58</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.96</v>
+        <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="P2" t="n">
-        <v>3.41</v>
+        <v>2.43</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.61</v>
+        <v>2.51</v>
       </c>
       <c r="O3" t="n">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="P3" t="n">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.51</v>
+        <v>1.96</v>
       </c>
       <c r="O6" t="n">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.58</v>
+        <v>3.41</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O8" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P8" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P9" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AU14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,27 +678,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46182.58333333334</v>
+        <v>46182.54166666666</v>
       </c>
     </row>
     <row r="3">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.96</v>
+        <v>2.61</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="P6" t="n">
-        <v>3.41</v>
+        <v>2.43</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1473,27 +1473,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="O7" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>3.06</v>
+        <v>3.41</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46182.66666666666</v>
+        <v>46182.58333333334</v>
       </c>
     </row>
     <row r="8">
@@ -1632,27 +1632,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>46182.79166666666</v>
+        <v>46182.625</v>
       </c>
     </row>
     <row r="9">
@@ -1791,27 +1791,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>46182.79166666666</v>
+        <v>46182.625</v>
       </c>
     </row>
     <row r="10">
@@ -1950,156 +1950,792 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CD Castellón</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="3" t="n">
+        <v>46182.66666666666</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Maghreb Fès</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>FAR Rabat</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="3" t="n">
+        <v>46182.70833333334</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="3" t="n">
+        <v>46182.79166666666</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="3" t="n">
+        <v>46182.79166666666</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Canada Canadian Premier League</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Atlético Ottawa</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Supra du Québec</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" s="3" t="n">
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="3" t="n">
         <v>46182.83333333334</v>
       </c>
     </row>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.51</v>
+        <v>2.34</v>
       </c>
       <c r="O3" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>2.58</v>
+        <v>2.83</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.83</v>
+        <v>3.41</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.96</v>
+        <v>2.51</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="P7" t="n">
-        <v>3.41</v>
+        <v>2.58</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P3" t="n">
-        <v>2.83</v>
+        <v>3.41</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.96</v>
+        <v>2.51</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="P5" t="n">
-        <v>3.41</v>
+        <v>2.58</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.61</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="P6" t="n">
-        <v>2.43</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.51</v>
+        <v>2.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="P7" t="n">
-        <v>2.58</v>
+        <v>2.43</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P12" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O13" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.96</v>
+        <v>2.51</v>
       </c>
       <c r="O3" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="P3" t="n">
-        <v>3.41</v>
+        <v>2.58</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P5" t="n">
-        <v>2.58</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="O6" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>3.41</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O12" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P12" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P13" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P12" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O13" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.54</v>
       </c>
       <c r="P4" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="O5" t="n">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.96</v>
+        <v>2.61</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="P6" t="n">
-        <v>3.41</v>
+        <v>2.43</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.61</v>
+        <v>1.96</v>
       </c>
       <c r="O7" t="n">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.43</v>
+        <v>3.41</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O12" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P12" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P13" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.51</v>
+        <v>2.34</v>
       </c>
       <c r="O3" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>2.58</v>
+        <v>2.83</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="O4" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>3.41</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.34</v>
+        <v>2.51</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="P5" t="n">
-        <v>2.83</v>
+        <v>2.58</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.61</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="P6" t="n">
-        <v>2.43</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.96</v>
+        <v>2.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="P7" t="n">
-        <v>3.41</v>
+        <v>2.43</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.25</v>
+        <v>2.61</v>
       </c>
       <c r="O6" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>2.43</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.61</v>
+        <v>2.25</v>
       </c>
       <c r="O7" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>2.43</v>
+        <v>2.89</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P12" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O13" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.34</v>
+        <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="P3" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.51</v>
+        <v>2.34</v>
       </c>
       <c r="O5" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>2.58</v>
+        <v>2.83</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.61</v>
+        <v>2.51</v>
       </c>
       <c r="O6" t="n">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="P6" t="n">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.61</v>
+        <v>2.34</v>
       </c>
       <c r="O3" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.96</v>
+        <v>2.51</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="P4" t="n">
-        <v>3.41</v>
+        <v>2.58</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.83</v>
+        <v>3.41</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.51</v>
+        <v>2.61</v>
       </c>
       <c r="O6" t="n">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="P6" t="n">
-        <v>2.58</v>
+        <v>2.43</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.34</v>
+        <v>2.51</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="P3" t="n">
-        <v>2.83</v>
+        <v>2.58</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.51</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>2.58</v>
+        <v>2.83</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.61</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="P6" t="n">
-        <v>2.43</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.25</v>
+        <v>2.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="P7" t="n">
-        <v>2.89</v>
+        <v>2.43</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O12" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P12" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P13" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.25</v>
+        <v>2.61</v>
       </c>
       <c r="O6" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>2.43</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.61</v>
+        <v>2.25</v>
       </c>
       <c r="O7" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>2.43</v>
+        <v>2.89</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P12" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O13" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.51</v>
+        <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="P3" t="n">
-        <v>2.58</v>
+        <v>2.43</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P4" t="n">
-        <v>2.83</v>
+        <v>3.41</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.96</v>
+        <v>2.34</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>3.41</v>
+        <v>2.83</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.61</v>
+        <v>2.51</v>
       </c>
       <c r="O6" t="n">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="P6" t="n">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O12" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P12" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P13" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.61</v>
+        <v>2.34</v>
       </c>
       <c r="O3" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.34</v>
+        <v>2.61</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="P5" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P6" t="n">
-        <v>2.58</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="P7" t="n">
-        <v>2.89</v>
+        <v>2.58</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.96</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>3.41</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.61</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>3.52</v>
+        <v>3.65</v>
       </c>
       <c r="P5" t="n">
-        <v>2.43</v>
+        <v>3.2</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.51</v>
+        <v>2.36</v>
       </c>
       <c r="O7" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="O10" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="P10" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P12" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O13" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P7" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O12" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P12" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P13" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,14 +1202,14 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P5" t="n">
         <v>3.2</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="O6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="O7" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P12" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O13" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P3" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="O5" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O12" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P12" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P13" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P5" t="n">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="O6" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="O10" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P10" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P12" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O13" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -887,10 +887,10 @@
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="P3" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1205,10 +1205,10 @@
         <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P6" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="O3" t="n">
-        <v>3.68</v>
+        <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>3.18</v>
+        <v>2.42</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="O4" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="P4" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="O5" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.83</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.38</v>
+        <v>3.68</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="P7" t="n">
-        <v>2.83</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="P5" t="n">
-        <v>2.83</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="O7" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>2.22</v>
+        <v>2.83</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O12" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P12" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P13" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
         <v>3.38</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
         <v>3.38</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="O6" t="n">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="P6" t="n">
-        <v>3.18</v>
+        <v>2.83</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="P7" t="n">
-        <v>2.83</v>
+        <v>3.18</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="O4" t="n">
-        <v>3.38</v>
+        <v>3.43</v>
       </c>
       <c r="P4" t="n">
-        <v>2.22</v>
+        <v>3.14</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="O6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.83</v>
+        <v>2.42</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="O7" t="n">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>3.18</v>
+        <v>2.83</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2003,7 +2003,7 @@
         <v>3.9</v>
       </c>
       <c r="P10" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>2.83</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.94</v>
+        <v>2.55</v>
       </c>
       <c r="O4" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="P4" t="n">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="O5" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.34</v>
+        <v>1.94</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="P7" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="P12" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O13" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="P3" t="n">
-        <v>2.83</v>
+        <v>2.22</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="O4" t="n">
         <v>3.38</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.41</v>
+        <v>1.98</v>
       </c>
       <c r="O5" t="n">
         <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.42</v>
+        <v>3.23</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="P6" t="n">
         <v>2.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.94</v>
+        <v>2.41</v>
       </c>
       <c r="O7" t="n">
-        <v>3.43</v>
+        <v>3.22</v>
       </c>
       <c r="P7" t="n">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.82</v>
+        <v>3.06</v>
       </c>
       <c r="P12" t="n">
-        <v>2.72</v>
+        <v>3.42</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.32</v>
+        <v>3.18</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>2.53</v>
       </c>
       <c r="P13" t="n">
-        <v>3.12</v>
+        <v>2.23</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="O3" t="n">
         <v>3.38</v>
       </c>
       <c r="P3" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.15</v>
+        <v>2.54</v>
       </c>
       <c r="O4" t="n">
         <v>3.38</v>
       </c>
       <c r="P4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P5" t="n">
-        <v>3.23</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.54</v>
+        <v>2.41</v>
       </c>
       <c r="O6" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.41</v>
+        <v>1.98</v>
       </c>
       <c r="O7" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>3.23</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
         <v>3.38</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="O5" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>3.23</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.41</v>
+        <v>2.54</v>
       </c>
       <c r="O6" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="P6" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.98</v>
+        <v>2.41</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="P7" t="n">
-        <v>3.23</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="O10" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="O12" t="n">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="P12" t="n">
-        <v>3.42</v>
+        <v>3.02</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.18</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
         <v>2.53</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="O4" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.22</v>
+        <v>3.23</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.98</v>
+        <v>2.41</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="P5" t="n">
-        <v>3.23</v>
+        <v>2.7</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
         <v>3.38</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.41</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="O3" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>2.48</v>
+        <v>3.23</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P4" t="n">
-        <v>3.23</v>
+        <v>2.22</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="O5" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="P5" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="O6" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.22</v>
+        <v>2.7</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="O13" t="n">
-        <v>2.53</v>
+        <v>2.79</v>
       </c>
       <c r="P13" t="n">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.76</v>
       </c>
       <c r="P3" t="n">
-        <v>3.23</v>
+        <v>3.16</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="O4" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>2.22</v>
+        <v>3.05</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="P5" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="P6" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="O7" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.95</v>
+        <v>2.43</v>
       </c>
       <c r="O3" t="n">
-        <v>3.76</v>
+        <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>3.16</v>
+        <v>2.42</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="P4" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="O5" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="O6" t="n">
-        <v>3.38</v>
+        <v>3.76</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>3.16</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="P7" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="O3" t="n">
-        <v>3.22</v>
+        <v>3.76</v>
       </c>
       <c r="P3" t="n">
-        <v>2.42</v>
+        <v>3.16</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="O4" t="n">
         <v>3.22</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P5" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
-        <v>3.76</v>
+        <v>3.22</v>
       </c>
       <c r="P6" t="n">
-        <v>3.16</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="O7" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.01</v>
+        <v>3.18</v>
       </c>
       <c r="O12" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="P12" t="n">
-        <v>3.02</v>
+        <v>2.49</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.18</v>
+        <v>2.01</v>
       </c>
       <c r="O13" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="P13" t="n">
-        <v>2.49</v>
+        <v>3.02</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.76</v>
+        <v>3.38</v>
       </c>
       <c r="P3" t="n">
-        <v>3.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
         <v>3.22</v>
       </c>
       <c r="P4" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="O5" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="O6" t="n">
         <v>3.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="P7" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.18</v>
+        <v>2.01</v>
       </c>
       <c r="O12" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="P12" t="n">
-        <v>2.49</v>
+        <v>3.02</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.01</v>
+        <v>3.18</v>
       </c>
       <c r="O13" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="P13" t="n">
-        <v>3.02</v>
+        <v>2.49</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="O3" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="O4" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.09</v>
+        <v>2.37</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.43</v>
+        <v>2.09</v>
       </c>
       <c r="O6" t="n">
-        <v>3.22</v>
+        <v>3.44</v>
       </c>
       <c r="P6" t="n">
-        <v>2.42</v>
+        <v>3.09</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.76</v>
+        <v>3.48</v>
       </c>
       <c r="P7" t="n">
-        <v>3.16</v>
+        <v>2.44</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
         <v>2.88</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.18</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
-        <v>2.79</v>
+        <v>2.53</v>
       </c>
       <c r="P13" t="n">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P7" t="n">
         <v>2.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.44</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>2.98</v>
       </c>
       <c r="O12" t="n">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="P12" t="n">
-        <v>3.02</v>
+        <v>2.23</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.98</v>
+        <v>2.01</v>
       </c>
       <c r="O13" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="P13" t="n">
-        <v>2.23</v>
+        <v>3.02</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="O14" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.33</v>
+        <v>3.59</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.62</v>
+        <v>2.09</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P4" t="n">
-        <v>2.49</v>
+        <v>3.09</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.09</v>
+        <v>2.37</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>3.09</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="P4" t="n">
-        <v>3.09</v>
+        <v>2.44</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="O5" t="n">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="P5" t="n">
-        <v>2.44</v>
+        <v>3.09</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.98</v>
+        <v>3.37</v>
       </c>
       <c r="O12" t="n">
-        <v>2.53</v>
+        <v>2.87</v>
       </c>
       <c r="P12" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P3" t="n">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O4" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="P5" t="n">
-        <v>3.09</v>
+        <v>2.44</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.37</v>
+        <v>1.91</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P8" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.37</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>3.37</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P13" t="n">
-        <v>3.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="O3" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>3.09</v>
+        <v>2.45</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P4" t="n">
-        <v>2.49</v>
+        <v>2.97</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="O5" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.37</v>
+        <v>1.97</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
         <v>1.85</v>
@@ -1841,10 +1841,10 @@
         <v>2.25</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
         <v>2.9</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>3.37</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.37</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>3.59</v>
+        <v>4.4</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.37</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>3.37</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P13" t="n">
-        <v>3.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="O4" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>2.97</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>2.97</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="P2" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.97</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.87</v>
+        <v>2.68</v>
       </c>
       <c r="P13" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="O2" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="P2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="P4" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.97</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-09.xlsx
+++ b/jogos_2026-06-09.xlsx
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -714,14 +714,14 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -786,12 +786,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46182.54166666666</v>
@@ -852,19 +852,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -873,25 +873,25 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P3" t="n">
         <v>2.45</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.62</v>
-      </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -945,12 +945,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51', '67']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['79', '90+7']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46182.58333333334</v>
@@ -1011,22 +1011,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -1039,17 +1039,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1104,14 +1104,14 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
+          <t>['14', '16', '29']</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46182.58333333334</v>
@@ -1170,25 +1170,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1198,17 +1198,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '42']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
@@ -1281,28 +1281,28 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46182.58333333334</v>
@@ -1329,139 +1329,139 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>['32']</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>2</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46182.58333333334</v>
@@ -1488,45 +1488,45 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '15', '29', '40']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '48']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
@@ -1599,28 +1599,28 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46182.58333333334</v>
@@ -1647,25 +1647,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1675,17 +1675,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
         <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AJ8" t="n">
@@ -1758,28 +1758,28 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46182.625</v>
@@ -1806,16 +1806,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1827,24 +1827,24 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
         <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1899,14 +1899,14 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
+          <t>['78', '90+1']</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
@@ -1917,28 +1917,28 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46182.625</v>
@@ -1974,36 +1974,36 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P10" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '80', '90+4']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57', '69']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
@@ -2076,28 +2076,28 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46182.66666666666</v>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2162,7 +2162,7 @@
         <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2235,28 +2235,28 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46182.70833333334</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
